--- a/benchmark/generated_files/RIC-2_V_041.xlsx
+++ b/benchmark/generated_files/RIC-2_V_041.xlsx
@@ -445,49 +445,35 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Filiale: SEDE CENTRALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Movimenti al 28/02/2026</t>
+          <t>Saldo iniziale: 20.963,70 EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Codice cliente: 547216</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Intestatario: Marco Rossi</t>
+          <t>Divisa: EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Divisa: EUR</t>
+          <t>IBAN: IT86 I069 5005 8000 0005 5123 456</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saldo iniziale: 19.131,86 EUR</t>
+          <t>Movimenti al 28/02/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Banca: Hype</t>
+          <t>Tipo conto: Carta ricaricabile</t>
         </is>
       </c>
     </row>
@@ -519,11 +505,11 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - ACI BOLLO AUTO TARGA MG224BS</t>
+          <t>Pagam. POS - PAGAMENTO POS 7,23 EUR DEL 01.01.2026 A (ITA) PRIMOR CATANIA</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-67.91</v>
+        <v>-7.23</v>
       </c>
       <c r="D11" s="3" t="n"/>
     </row>
@@ -533,445 +519,445 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:214313135 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3729 VEGA CARBURANTI</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-52.76</v>
+        <v>-69.42</v>
       </c>
       <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>-7.82</v>
-      </c>
-      <c r="D13" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>163.59</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 11,57 EUR DEL 04.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 111,89 EUR DEL 02.01.2026 A (ITA) LIDL ITALIA SRL</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-11.57</v>
+        <v>-111.89</v>
       </c>
       <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 57,10 EUR DEL 04.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-57.1</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 19,95 EUR DEL 05.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2302 AVIA MODENA</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-19.95</v>
+        <v>-120.51</v>
       </c>
       <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 51,50 EUR DEL 06.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-51.5</v>
+        <v>-11.5</v>
       </c>
       <c r="D17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46029</v>
+        <v>46026</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 77,76 EUR DEL 07.01.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>Pagam. POS - PAGAMENTO POS 60,39 EUR DEL 04.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-77.76000000000001</v>
+        <v>-60.39</v>
       </c>
       <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - ACI BOLLO AUTO TARGA YA126JJ</t>
+          <t>Pagam. POS - PAGAMENTO POS 134,68 EUR DEL 05.01.2026 A (ITA) MARGHERITA CONAD</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-36.75</v>
+        <v>-134.68</v>
       </c>
       <c r="D19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46031</v>
+        <v>46027</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 86,79 EUR DEL 09.01.2026 A (ITA) ESSELUNGA MILANO</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>-86.79000000000001</v>
-      </c>
-      <c r="D20" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>296.26</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46031</v>
+        <v>46028</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 28,89 EUR DEL 09.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4562 POMPE BIANCHE</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-28.89</v>
+        <v>-80.01000000000001</v>
       </c>
       <c r="D21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46031</v>
+        <v>46028</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-217423038</t>
+          <t>Pagam. POS - PAGAMENTO POS 15,19 EUR DEL 06.01.2026 A (ITA) COOP LOMBARDIA</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-13.37</v>
+        <v>-15.19</v>
       </c>
       <c r="D22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 45,50 EUR DEL 11.01.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 173,90 EUR DEL 07.01.2026 A (ITA) MACELLERIA BONI</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-45.5</v>
+        <v>-173.9</v>
       </c>
       <c r="D23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46035</v>
+        <v>46031</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n">
-        <v>183.06</v>
-      </c>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1012 COSTANTIN</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-35.57</v>
+      </c>
+      <c r="D24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46036</v>
+        <v>46031</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 25,76 EUR DEL 14.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 123,31 EUR DEL 09.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-25.76</v>
+        <v>-123.31</v>
       </c>
       <c r="D25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n">
-        <v>217.41</v>
-      </c>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6270 PRIMOR</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-48.58</v>
+      </c>
+      <c r="D26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46039</v>
+        <v>46033</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-24.74</v>
+        <v>-14.73</v>
       </c>
       <c r="D27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46044</v>
+        <v>46034</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 70,67 EUR DEL 22.01.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 5,57 EUR DEL 12.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-70.67</v>
+        <v>-5.57</v>
       </c>
       <c r="D28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46044</v>
+        <v>46035</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 34,71 EUR DEL 22.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1426 COLOURS &amp; BEAUTY</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-34.71</v>
+        <v>-30.13</v>
       </c>
       <c r="D29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46044</v>
+        <v>46036</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 51,78 EUR DEL 22.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 53,25 EUR DEL 14.01.2026 A (ITA) ENI SHOP</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-51.78</v>
+        <v>-53.25</v>
       </c>
       <c r="D30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n">
-        <v>244.48</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 71,11 EUR DEL 15.01.2026 A (ITA) DISTRIBUTORE ENI</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-71.11</v>
+      </c>
+      <c r="D31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46045</v>
+        <v>46039</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Addebito SDD - JUST EAT ITALY SRL</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-16.95</v>
+        <v>-30.76</v>
       </c>
       <c r="D32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 91,15 EUR DEL 18.01.2026 A (ITA) MACELLERIA BONI</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-66.23999999999999</v>
+        <v>-91.15000000000001</v>
       </c>
       <c r="D33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46046</v>
+        <v>46040</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2652 CONAD SUPERSTORE</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-12.27</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="D34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46046</v>
+        <v>46041</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 71,09 EUR DEL 19.01.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-76.29000000000001</v>
+        <v>-71.09</v>
       </c>
       <c r="D35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n">
-        <v>76.17</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 40,93 EUR DEL 22.01.2026 A (ITA) EKOM CORSICO</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-40.93</v>
+      </c>
+      <c r="D36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 40,66 EUR DEL 27.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 41,48 EUR DEL 22.01.2026 A (ITA) ESSELUNGA MILANO</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-40.66</v>
+        <v>-41.48</v>
       </c>
       <c r="D37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46049</v>
+        <v>46045</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-210215612</t>
+          <t>Pagam. POS - PAGAMENTO POS 53,55 EUR DEL 23.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>-5.65</v>
+        <v>-53.55</v>
       </c>
       <c r="D38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46050</v>
+        <v>46045</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 13,20 EUR DEL 28.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="D39" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>293.88</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46050</v>
+        <v>46046</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 67,52 EUR DEL 28.01.2026 A (ITA) ITALO NTV S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 11,87 EUR DEL 24.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-67.52</v>
+        <v>-11.87</v>
       </c>
       <c r="D40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46050</v>
+        <v>46046</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>-96.06999999999999</v>
-      </c>
-      <c r="D41" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
+        <v>217.28</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46051</v>
+        <v>46049</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>-7.81</v>
-      </c>
-      <c r="D42" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>297.67</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 13,25 EUR DEL 29.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4685 ARD DISCOUNT</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-13.25</v>
+        <v>-138.09</v>
       </c>
       <c r="D43" s="3" t="n"/>
     </row>
@@ -981,67 +967,67 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 5,39 EUR DEL 30.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 41,83 EUR DEL 30.01.2026 A (ITA) WYCON COSMETICS</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>-5.39</v>
+        <v>-41.83</v>
       </c>
       <c r="D44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 64,58 EUR DEL 30.01.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>Pagam. POS - PAGAMENTO POS 42,12 EUR DEL 31.01.2026 A (ITA) STAZIONE Q8</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>-64.58</v>
+        <v>-42.12</v>
       </c>
       <c r="D45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Pagam. POS - PAGAMENTO POS 29,11 EUR DEL 01.02.2026 A (ITA) BILLY TACOS VOMERO</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-8.460000000000001</v>
+        <v>-29.11</v>
       </c>
       <c r="D46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:215452440 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Pagam. POS - PAGAMENTO POS 82,84 EUR DEL 02.02.2026 A (ITA) HISTOIRE D'OR</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>-95.39</v>
+        <v>-82.84</v>
       </c>
       <c r="D47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46057</v>
+        <v>46056</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 41,89 EUR DEL 04.02.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Pagam. POS - PAGAMENTO POS 59,28 EUR DEL 03.02.2026 A (ITA) SÌ CON TE PADOVA</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>-41.89</v>
+        <v>-59.28</v>
       </c>
       <c r="D48" s="3" t="n"/>
     </row>
@@ -1051,27 +1037,27 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n">
-        <v>89.27</v>
-      </c>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5735 DPIÙ TORINO</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>-131.19</v>
+      </c>
+      <c r="D49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>-92.04000000000001</v>
-      </c>
-      <c r="D50" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
+        <v>186.54</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -1079,13 +1065,13 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n">
-        <v>152.65</v>
-      </c>
+          <t>Addebito SDD - TELEPASS S.P.A. PEDAGGI</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>-52.67</v>
+      </c>
+      <c r="D51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -1093,115 +1079,115 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-214952737</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>-33.09</v>
+        <v>-14.34</v>
       </c>
       <c r="D52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 79,73 EUR DEL 08.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>-79.73</v>
-      </c>
-      <c r="D53" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0075849</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>284.88</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 8463 TRATTORIA LA PERGOLA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>-46.33</v>
+        <v>-5.24</v>
       </c>
       <c r="D54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 164,58 EUR DEL 11.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 37,09 EUR DEL 09.02.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>-164.58</v>
+        <v>-37.09</v>
       </c>
       <c r="D55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46068</v>
+        <v>46063</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7427 MERCATÒ EXTRA NORD</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>-7.45</v>
+        <v>-51.46</v>
       </c>
       <c r="D56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46068</v>
+        <v>46064</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n">
-        <v>53.26</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 23,95 EUR DEL 11.02.2026 A (ITA) BAR CENTRALE</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>-23.95</v>
+      </c>
+      <c r="D57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46069</v>
+        <v>46064</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 82,30 EUR DEL 11.02.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>-26.37</v>
+        <v>-82.3</v>
       </c>
       <c r="D58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46069</v>
+        <v>46064</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4770 ESSELUNGA S.P.A.</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>-8.48</v>
+        <v>-112.69</v>
       </c>
       <c r="D59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46069</v>
+        <v>46064</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -1210,90 +1196,90 @@
       </c>
       <c r="C60" s="3" t="n"/>
       <c r="D60" s="3" t="n">
-        <v>129.34</v>
+        <v>91.83</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46070</v>
+        <v>46067</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 71,08 EUR DEL 17.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 71,38 EUR DEL 14.02.2026 A (ITA) ROADHOUSE</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>-71.08</v>
+        <v>-71.38</v>
       </c>
       <c r="D61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46070</v>
+        <v>46067</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 21,80 EUR DEL 17.02.2026 A (ITA) TABACCHERIA N.12</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>-21.8</v>
-      </c>
-      <c r="D62" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>50.01</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46070</v>
+        <v>46068</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 105,69 EUR DEL 17.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4158 RETITALIA</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>-105.69</v>
+        <v>-31.5</v>
       </c>
       <c r="D63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46072</v>
+        <v>46069</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 14,44 EUR DEL 19.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6756 THUN MARGHERA</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>-14.44</v>
+        <v>-43.82</v>
       </c>
       <c r="D64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46072</v>
+        <v>46070</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2004 ROSSOPOMODORO NAPOLI</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>-6.7</v>
+        <v>-25.17</v>
       </c>
       <c r="D65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46072</v>
+        <v>46070</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 56,85 EUR DEL 19.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6423 WOK TO WALK</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>-56.85</v>
+        <v>-32.59</v>
       </c>
       <c r="D66" s="3" t="n"/>
     </row>
@@ -1303,25 +1289,25 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0075849</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n">
-        <v>205.12</v>
-      </c>
+          <t>Disposizione - RIF:217120033 BEN. TINTORIA RAPIDA CENTRO</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>-63.53</v>
+      </c>
+      <c r="D67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 20,79 EUR DEL 20.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3089 KEBHOUZE</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>-20.79</v>
+        <v>-23.79</v>
       </c>
       <c r="D68" s="3" t="n"/>
     </row>
@@ -1331,25 +1317,25 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>-62.28</v>
-      </c>
-      <c r="D69" s="3" t="n"/>
+          <t>RICARICA HYPE DA CONTO 0123456</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>62.78</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 33,62 EUR DEL 21.02.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 16,29 EUR DEL 22.02.2026 A (ITA) MCDONALD'S ITALIA</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>-33.62</v>
+        <v>-16.29</v>
       </c>
       <c r="D70" s="3" t="n"/>
     </row>
@@ -1359,53 +1345,53 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Pagam. POS - PAGAMENTO POS 105,98 EUR DEL 23.02.2026 A (ITA) MACELLERIA BONI</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>-12.18</v>
+        <v>-105.98</v>
       </c>
       <c r="D71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 162,56 EUR DEL 24.02.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Pagam. POS - PAGAMENTO POS 133,26 EUR DEL 25.02.2026 A (ITA) UNES</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>-162.56</v>
+        <v>-133.26</v>
       </c>
       <c r="D72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>RICARICA HYPE DA CONTO 0123456</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n">
-        <v>217.17</v>
-      </c>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3114 MIGROS PADOVA</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>-135.67</v>
+      </c>
+      <c r="D73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Pagam. POS - PAGAMENTO POS 77,21 EUR DEL 25.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>-8.949999999999999</v>
+        <v>-77.20999999999999</v>
       </c>
       <c r="D74" s="3" t="n"/>
     </row>
@@ -1415,18 +1401,18 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 20,83 EUR DEL 28.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2426 NATURA</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>-20.83</v>
+        <v>-90.64</v>
       </c>
       <c r="D75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Saldo finale: 1.082,08 EUR</t>
+          <t>Saldo finale: 10.297,91 EUR</t>
         </is>
       </c>
     </row>
